--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.96963332044817</v>
+        <v>12.02006541457283</v>
       </c>
       <c r="D2" t="n">
-        <v>73.88722874340004</v>
+        <v>12.00667467080251</v>
       </c>
       <c r="E2" t="n">
-        <v>21.3335552665417</v>
+        <v>3.466702730813026</v>
       </c>
       <c r="F2" t="n">
-        <v>22.23199601830726</v>
+        <v>3.61269935297493</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.78757785131902</v>
+        <v>3.377981400839341</v>
       </c>
       <c r="D3" t="n">
-        <v>20.43757303385962</v>
+        <v>3.321105618002189</v>
       </c>
       <c r="E3" t="n">
-        <v>21.3335552665417</v>
+        <v>3.466702730813026</v>
       </c>
       <c r="F3" t="n">
-        <v>22.23199601830726</v>
+        <v>3.61269935297493</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.00356304402262</v>
+        <v>5.363078994653676</v>
       </c>
       <c r="D4" t="n">
-        <v>32.6443277469447</v>
+        <v>5.304703258878515</v>
       </c>
       <c r="E4" t="n">
-        <v>21.3335552665417</v>
+        <v>3.466702730813026</v>
       </c>
       <c r="F4" t="n">
-        <v>22.23199601830726</v>
+        <v>3.61269935297493</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.9849601832134</v>
+        <v>4.710056029772178</v>
       </c>
       <c r="D5" t="n">
-        <v>24.23324163210527</v>
+        <v>3.937901765217106</v>
       </c>
       <c r="E5" t="n">
-        <v>21.3335552665417</v>
+        <v>3.466702730813026</v>
       </c>
       <c r="F5" t="n">
-        <v>22.23199601830726</v>
+        <v>3.61269935297493</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.40613174920725</v>
+        <v>10.14099640924618</v>
       </c>
       <c r="D6" t="n">
-        <v>62.46319405435761</v>
+        <v>10.15026903383311</v>
       </c>
       <c r="E6" t="n">
-        <v>21.3335552665417</v>
+        <v>3.466702730813026</v>
       </c>
       <c r="F6" t="n">
-        <v>22.23199601830726</v>
+        <v>3.61269935297493</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.85731872416601</v>
+        <v>11.51431429267698</v>
       </c>
       <c r="D7" t="n">
-        <v>70.97340180887545</v>
+        <v>11.53317779394226</v>
       </c>
       <c r="E7" t="n">
-        <v>21.3335552665417</v>
+        <v>3.466702730813026</v>
       </c>
       <c r="F7" t="n">
-        <v>22.23199601830726</v>
+        <v>3.61269935297493</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
